--- a/public/plantillas/pedido-pumping-limpieza-bes-4368.xlsx
+++ b/public/plantillas/pedido-pumping-limpieza-bes-4368.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -436,13 +436,12 @@
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Plantilla de pedido de ejemplo — formato AS2 Pedido Cliente (columna G opcional: Cantidad fija)</t>
+          <t>Plantilla de pedido de ejemplo — formato AS2 Pedido Cliente</t>
         </is>
       </c>
     </row>
@@ -508,11 +507,6 @@
           <t>Porcentaje Descuento</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Cantidad fija</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -539,11 +533,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -570,11 +559,6 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -601,11 +585,6 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -632,11 +611,6 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -663,11 +637,6 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,11 +663,6 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -725,11 +689,6 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -756,11 +715,6 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -787,11 +741,6 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -818,11 +767,6 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -849,11 +793,6 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -880,11 +819,6 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -911,11 +845,6 @@
       <c r="F17" t="n">
         <v>0</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -942,11 +871,6 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -973,11 +897,6 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1004,11 +923,6 @@
       <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1035,11 +949,6 @@
       <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1066,11 +975,6 @@
       <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1097,11 +1001,6 @@
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1128,11 +1027,6 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1159,11 +1053,6 @@
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1190,11 +1079,6 @@
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1221,11 +1105,6 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1252,11 +1131,6 @@
       <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1283,11 +1157,6 @@
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1314,11 +1183,6 @@
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1345,11 +1209,6 @@
       <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1376,11 +1235,6 @@
       <c r="F32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1407,11 +1261,6 @@
       <c r="F33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1438,11 +1287,6 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1469,11 +1313,6 @@
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1500,11 +1339,6 @@
       <c r="F36" t="n">
         <v>0</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1531,11 +1365,6 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1562,11 +1391,6 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1593,11 +1417,6 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1624,11 +1443,6 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1654,11 +1468,6 @@
       </c>
       <c r="F41" t="n">
         <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
       </c>
     </row>
   </sheetData>
